--- a/7-Export/Sample Output/Report.xlsx
+++ b/7-Export/Sample Output/Report.xlsx
@@ -12,12 +12,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>ResourceName</t>
   </si>
   <si>
     <t>ResourceType</t>
+  </si>
+  <si>
+    <t>Sku</t>
   </si>
   <si>
     <t>OriginRegion</t>
@@ -74,14 +77,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AvailabilityReport" displayName="AvailabilityReport" ref="A1:E2" headerRowCount="1">
-  <autoFilter ref="A1:E2"/>
-  <tableColumns count="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AvailabilityReport" displayName="AvailabilityReport" ref="A1:F2" headerRowCount="1">
+  <autoFilter ref="A1:F2"/>
+  <tableColumns count="6">
     <tableColumn id="1" name="ResourceName"/>
     <tableColumn id="2" name="ResourceType"/>
-    <tableColumn id="3" name="OriginRegion"/>
-    <tableColumn id="4" name="TargetRegion"/>
-    <tableColumn id="5" name="IsAvailableInTargetRegion"/>
+    <tableColumn id="3" name="Sku"/>
+    <tableColumn id="4" name="OriginRegion"/>
+    <tableColumn id="5" name="TargetRegion"/>
+    <tableColumn id="6" name="IsAvailableInTargetRegion"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -89,14 +93,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.98710060119629" customWidth="1"/>
     <col min="2" max="2" width="32.97323989868164" customWidth="1"/>
-    <col min="3" max="3" width="15.011561393737793" customWidth="1"/>
-    <col min="4" max="4" width="15.340988159179688" customWidth="1"/>
-    <col min="5" max="5" width="26.389070510864258" customWidth="1"/>
+    <col min="3" max="3" width="9.140625" customWidth="1"/>
+    <col min="4" max="4" width="15.011561393737793" customWidth="1"/>
+    <col min="5" max="5" width="15.340988159179688" customWidth="1"/>
+    <col min="6" max="6" width="26.389070510864258" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -115,10 +120,13 @@
       <c r="E1" s="0" t="s">
         <v>4</v>
       </c>
+      <c r="F1" s="0" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="2">
       <c r="B2" s="0" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
